--- a/docs/remapare-propusa.xlsx
+++ b/docs/remapare-propusa.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="160">
   <si>
     <t>Model</t>
   </si>
@@ -184,21 +184,6 @@
     <t>00020394  PAL S 16 MM 2800X2070 (MP)  nume 53%  · folosit la acest produs</t>
   </si>
   <si>
-    <t>MDF 4MM</t>
-  </si>
-  <si>
-    <t>00010419  MDF 4MM (BUC)</t>
-  </si>
-  <si>
-    <t>00006805  MDF BRUT 4MM (MP)  nume 70%  · folosit la acest produs</t>
-  </si>
-  <si>
-    <t>00015935  MDF BRUT 6MM (MP)  nume 52%</t>
-  </si>
-  <si>
-    <t>00018396  MDF BRUT 8MM (MP)  nume 52%</t>
-  </si>
-  <si>
     <t>00015947  VATELINA SBRE 200 GR/230 H (MP)  nume 58%  · folosit la acest produs</t>
   </si>
   <si>
@@ -229,9 +214,6 @@
     <t>00023454  PAL 15 MM (MP)  nume 73%  · folosit la acest produs</t>
   </si>
   <si>
-    <t>00015935  MDF BRUT 6MM (MP)  nume 52%  · folosit la acest produs</t>
-  </si>
-  <si>
     <t>00002650  ADEZIV EDR ROSU (KG)  nume 56%  · folosit la acest produs</t>
   </si>
   <si>
@@ -244,9 +226,6 @@
     <t>CANAPEA-CORINA-II</t>
   </si>
   <si>
-    <t>00006805  MDF BRUT 4MM (MP)  nume 70%</t>
-  </si>
-  <si>
     <t>CANAPEA-DUBLA-CUBIC</t>
   </si>
   <si>
@@ -275,21 +254,6 @@
   </si>
   <si>
     <t>00000403  PAL 12 MM (MP)  nume 73%  · folosit la acest produs</t>
-  </si>
-  <si>
-    <t>CAPSE 80/12</t>
-  </si>
-  <si>
-    <t>00009232  CAPSE 80/12 (CUT)</t>
-  </si>
-  <si>
-    <t>00017332  CAPSE TAPITERIE 80X12 CH (1000B)  nume 62%  · folosit la acest produs</t>
-  </si>
-  <si>
-    <t>00006350  CAPSE 380/12 E-NEW (MIIB)  nume 61%  · folosit la acest produs</t>
-  </si>
-  <si>
-    <t>00001943  CAPSE 380/16 E (MIIB)  nume 55%  · folosit la acest produs</t>
   </si>
   <si>
     <t>PERNA SAMOBI</t>
@@ -916,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1459,34 +1423,34 @@
         <v>55</v>
       </c>
       <c r="B16" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I16">
-        <v>1102</v>
+        <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1494,34 +1458,34 @@
         <v>55</v>
       </c>
       <c r="B17" s="1">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="2">
         <v>15</v>
       </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.25</v>
-      </c>
       <c r="F17" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17">
         <v>22</v>
       </c>
-      <c r="I17">
-        <v>50</v>
-      </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="K17" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1529,171 +1493,171 @@
         <v>55</v>
       </c>
       <c r="B18" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2">
-        <v>15</v>
+        <v>0.3</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="H18" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="I18">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="K18" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B19" s="1">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19">
+        <v>230</v>
+      </c>
+      <c r="J19" t="s">
         <v>65</v>
       </c>
-      <c r="D19" t="s">
+      <c r="K19" t="s">
         <v>66</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B20" s="1">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2">
-        <v>1.7</v>
+        <v>0.25</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I20">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="J20" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K20" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B21" s="1">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2">
-        <v>1.44</v>
+        <v>0.05</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="H21" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="I21">
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="K21" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="1">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="1">
-        <v>19</v>
-      </c>
-      <c r="C22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" t="s">
-        <v>73</v>
-      </c>
       <c r="I22">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J22" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="K22" t="s">
         <v>14</v>
@@ -1701,69 +1665,69 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E23" s="2">
-        <v>0.05</v>
+        <v>1.7</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2">
-        <v>2.1</v>
+        <v>0.25</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H24" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="I24">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="J24" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="K24" t="s">
         <v>14</v>
@@ -1771,104 +1735,104 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B25" s="1">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2">
-        <v>1.7</v>
+        <v>0.064</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I25">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K25" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="2">
-        <v>1.7</v>
+        <v>10.1</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="H26" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="I26">
-        <v>1102</v>
+        <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="K26" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B27" s="1">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2">
-        <v>0.25</v>
+        <v>1.4</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I27">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K27" t="s">
         <v>14</v>
@@ -1876,104 +1840,104 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2">
-        <v>0.064</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="J28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E29" s="2">
-        <v>10.1</v>
+        <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H29" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I29">
-        <v>4</v>
+        <v>410</v>
       </c>
       <c r="J29" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K29" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I30">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="J30" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K30" t="s">
         <v>14</v>
@@ -1981,80 +1945,80 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" s="1">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0.24</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="1">
-        <v>2</v>
-      </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="2">
-        <v>4</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
       <c r="I31">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K31" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B32" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E32" s="2">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="I32">
-        <v>410</v>
+        <v>230</v>
       </c>
       <c r="J32" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" t="s">
         <v>80</v>
-      </c>
-      <c r="K32" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
         <v>19</v>
@@ -2063,7 +2027,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="2">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>14</v>
@@ -2072,7 +2036,7 @@
         <v>21</v>
       </c>
       <c r="H33" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="I33">
         <v>50</v>
@@ -2086,31 +2050,31 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
         <v>23</v>
       </c>
-      <c r="C34" t="s">
-        <v>82</v>
-      </c>
       <c r="D34" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="E34" s="2">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="I34">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J34" t="s">
         <v>14</v>
@@ -2121,136 +2085,136 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B35" s="1">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I35">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="J35" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="K35" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B36" s="1">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="I36">
-        <v>1102</v>
+        <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K36" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B37" s="1">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E37" s="2">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I37">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="J37" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="K37" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B38" s="1">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J38" t="s">
         <v>14</v>
@@ -2261,45 +2225,45 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B39" s="1">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>24</v>
       </c>
       <c r="E39" s="2">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G39" t="s">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="H39" t="s">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="I39">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="K39" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B40" s="1">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
         <v>31</v>
@@ -2308,7 +2272,7 @@
         <v>32</v>
       </c>
       <c r="E40" s="2">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>14</v>
@@ -2317,13 +2281,13 @@
         <v>33</v>
       </c>
       <c r="H40" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="I40">
         <v>85</v>
       </c>
       <c r="J40" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="K40" t="s">
         <v>14</v>
@@ -2331,139 +2295,139 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B41" s="1">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" t="s">
+        <v>64</v>
+      </c>
+      <c r="I41">
+        <v>230</v>
+      </c>
+      <c r="J41" t="s">
+        <v>65</v>
+      </c>
+      <c r="K41" t="s">
         <v>66</v>
-      </c>
-      <c r="E41" s="2">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" t="s">
-        <v>94</v>
-      </c>
-      <c r="H41" t="s">
-        <v>95</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="J41" t="s">
-        <v>14</v>
-      </c>
-      <c r="K41" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B42" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E42" s="2">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I42">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="J42" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K42" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B43" s="1">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E43" s="2">
-        <v>1.44</v>
+        <v>0.05</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="H43" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="I43">
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K43" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B44" s="1">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E44" s="2">
-        <v>0.24</v>
+        <v>2.1</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H44" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I44">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J44" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="K44" t="s">
         <v>14</v>
@@ -2471,69 +2435,69 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B45" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="D45" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E45" s="2">
-        <v>0.06</v>
+        <v>0.8</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J45" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B46" s="1">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E46" s="2">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H46" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="I46">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="K46" t="s">
         <v>14</v>
@@ -2541,174 +2505,174 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B47" s="1">
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="D47" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="2">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="I47">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c r="J47" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B48" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2">
-        <v>1.56</v>
+        <v>0.3</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="H48" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I48">
-        <v>1102</v>
+        <v>50</v>
       </c>
       <c r="J48" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="K48" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B49" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="D49" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E49" s="2">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H49" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="I49">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="J49" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="K49" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B50" s="1">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E50" s="2">
-        <v>0.05</v>
+        <v>2.6</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="J50" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="K50" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B51" s="1">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D51" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2">
-        <v>2.1</v>
+        <v>0.25</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H51" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I51">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="J51" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="K51" t="s">
         <v>14</v>
@@ -2716,69 +2680,69 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B52" s="1">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E52" s="2">
-        <v>0.8</v>
+        <v>0.05</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G52" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H52" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="I52">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="K52" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B53" s="1">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E53" s="2">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G53" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H53" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J53" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="K53" t="s">
         <v>14</v>
@@ -2786,10 +2750,10 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B54" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C54" t="s">
         <v>105</v>
@@ -2798,7 +2762,7 @@
         <v>13</v>
       </c>
       <c r="E54" s="2">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>14</v>
@@ -2807,185 +2771,185 @@
         <v>106</v>
       </c>
       <c r="H54" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="I54">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="J54" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="K54" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B55" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E55" s="2">
-        <v>0.3</v>
+        <v>1.916</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I55">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="J55" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="K55" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B56" s="1">
+        <v>17</v>
+      </c>
+      <c r="C56" t="s">
         <v>19</v>
       </c>
-      <c r="C56" t="s">
-        <v>111</v>
-      </c>
       <c r="D56" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H56" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="I56">
-        <v>410</v>
+        <v>50</v>
       </c>
       <c r="J56" t="s">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="K56" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B57" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E57" s="2">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H57" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="I57">
-        <v>230</v>
+        <v>410</v>
       </c>
       <c r="J57" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="K57" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B58" s="1">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E58" s="2">
-        <v>1.56</v>
+        <v>0.4</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="H58" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="I58">
-        <v>1102</v>
+        <v>382</v>
       </c>
       <c r="J58" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="K58" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B59" s="1">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E59" s="2">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H59" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="I59">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J59" t="s">
         <v>14</v>
@@ -2996,112 +2960,112 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" s="1">
+        <v>48</v>
+      </c>
+      <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
+        <v>49</v>
+      </c>
+      <c r="E60" s="2">
+        <v>1</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" t="s">
+        <v>113</v>
+      </c>
+      <c r="H60" t="s">
+        <v>114</v>
+      </c>
+      <c r="I60">
+        <v>29</v>
+      </c>
+      <c r="J60" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="1">
-        <v>28</v>
-      </c>
-      <c r="C60" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" t="s">
-        <v>25</v>
-      </c>
-      <c r="H60" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60" t="s">
-        <v>14</v>
-      </c>
       <c r="K60" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B61" s="1">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E61" s="2">
-        <v>2.1</v>
+        <v>19</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="I61">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="J61" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K61" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B62" s="1">
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="2">
-        <v>0.4</v>
+        <v>20</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G62" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J62" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K62" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B63" s="1">
         <v>5</v>
@@ -3113,7 +3077,7 @@
         <v>13</v>
       </c>
       <c r="E63" s="2">
-        <v>1.916</v>
+        <v>3.5</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>14</v>
@@ -3122,360 +3086,360 @@
         <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="I63">
         <v>230</v>
       </c>
       <c r="J63" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B64" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E64" s="2">
-        <v>2.32</v>
+        <v>0.5</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I64">
-        <v>1102</v>
+        <v>50</v>
       </c>
       <c r="J64" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="K64" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B65" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E65" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I65">
+        <v>410</v>
+      </c>
+      <c r="J65" t="s">
         <v>73</v>
       </c>
-      <c r="I65">
-        <v>50</v>
-      </c>
-      <c r="J65" t="s">
-        <v>14</v>
-      </c>
       <c r="K65" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B66" s="1">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="D66" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E66" s="2">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G66" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="H66" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="I66">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="J66" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K66" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>119</v>
+      </c>
+      <c r="B67" s="1">
+        <v>34</v>
+      </c>
+      <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
+        <v>49</v>
+      </c>
+      <c r="E67" s="2">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" t="s">
+        <v>113</v>
+      </c>
+      <c r="H67" t="s">
+        <v>123</v>
+      </c>
+      <c r="I67">
+        <v>29</v>
+      </c>
+      <c r="J67" t="s">
+        <v>124</v>
+      </c>
+      <c r="K67" t="s">
         <v>116</v>
-      </c>
-      <c r="B67" s="1">
-        <v>42</v>
-      </c>
-      <c r="C67" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" t="s">
-        <v>120</v>
-      </c>
-      <c r="H67" t="s">
-        <v>121</v>
-      </c>
-      <c r="I67">
-        <v>382</v>
-      </c>
-      <c r="J67" t="s">
-        <v>122</v>
-      </c>
-      <c r="K67" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B68" s="1">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="2">
         <v>24</v>
       </c>
-      <c r="E68" s="2">
-        <v>0.05</v>
-      </c>
       <c r="F68" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J68" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K68" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B69" s="1">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="I69">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="J69" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="K69" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B70" s="1">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D70" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E70" s="2">
-        <v>19</v>
+        <v>0.7</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="I70">
-        <v>183</v>
+        <v>50</v>
       </c>
       <c r="J70" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="K70" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B71" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E71" s="2">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H71" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>410</v>
       </c>
       <c r="J71" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K71" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B72" s="1">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E72" s="2">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="I72">
-        <v>230</v>
+        <v>382</v>
       </c>
       <c r="J72" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="K72" t="s">
-        <v>18</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B73" s="1">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D73" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E73" s="2">
-        <v>0.5</v>
+        <v>0.088</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G73" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H73" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I73">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J73" t="s">
         <v>14</v>
@@ -3486,115 +3450,115 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B74" s="1">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="D74" t="s">
         <v>49</v>
       </c>
       <c r="E74" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G74" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="H74" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="I74">
-        <v>410</v>
+        <v>29</v>
       </c>
       <c r="J74" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="K74" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B75" s="1">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E75" s="2">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G75" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="I75">
-        <v>382</v>
+        <v>230</v>
       </c>
       <c r="J75" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="K75" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B76" s="1">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E76" s="2">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G76" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="H76" t="s">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="I76">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="J76" t="s">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="K76" t="s">
-        <v>128</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B77" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C77" t="s">
         <v>26</v>
@@ -3603,7 +3567,7 @@
         <v>13</v>
       </c>
       <c r="E77" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>14</v>
@@ -3626,165 +3590,165 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B78" s="1">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C78" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E78" s="2">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H78" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I78">
-        <v>230</v>
+        <v>410</v>
       </c>
       <c r="J78" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="K78" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B79" s="1">
+        <v>5</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3.232</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79">
+        <v>230</v>
+      </c>
+      <c r="J79" t="s">
         <v>17</v>
       </c>
-      <c r="C79" t="s">
-        <v>19</v>
-      </c>
-      <c r="D79" t="s">
-        <v>20</v>
-      </c>
-      <c r="E79" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G79" t="s">
-        <v>21</v>
-      </c>
-      <c r="H79" t="s">
-        <v>22</v>
-      </c>
-      <c r="I79">
-        <v>50</v>
-      </c>
-      <c r="J79" t="s">
-        <v>14</v>
-      </c>
       <c r="K79" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B80" s="1">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C80" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D80" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E80" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="I80">
-        <v>410</v>
+        <v>50</v>
       </c>
       <c r="J80" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="K80" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B81" s="1">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C81" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="D81" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E81" s="2">
-        <v>2.1</v>
+        <v>10</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="H81" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="I81">
-        <v>382</v>
+        <v>4</v>
       </c>
       <c r="J81" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="K81" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B82" s="1">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E82" s="2">
-        <v>0.088</v>
+        <v>0.06</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="H82" t="s">
         <v>14</v>
@@ -3801,314 +3765,314 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B83" s="1">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="C83" t="s">
-        <v>124</v>
+        <v>12</v>
       </c>
       <c r="D83" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E83" s="2">
-        <v>3</v>
+        <v>3.232</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="I83">
-        <v>29</v>
+        <v>230</v>
       </c>
       <c r="J83" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B84" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C84" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E84" s="2">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I84">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="J84" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K84" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B85" s="1">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D85" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E85" s="2">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H85" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I85">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="J85" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K85" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B86" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
         <v>15</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G86" t="s">
-        <v>27</v>
-      </c>
       <c r="H86" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I86">
-        <v>4</v>
+        <v>230</v>
       </c>
       <c r="J86" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K86" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B87" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C87" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D87" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E87" s="2">
-        <v>2.4</v>
+        <v>20</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="I87">
-        <v>410</v>
+        <v>4</v>
       </c>
       <c r="J87" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="K87" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B88" s="1">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E88" s="2">
-        <v>3.232</v>
+        <v>0.1</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G88" t="s">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I88">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="J88" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K88" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B89" s="1">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E89" s="2">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H89" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="I89">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="J89" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="K89" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B90" s="1">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C90" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D90" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E90" s="2">
-        <v>10</v>
+        <v>0.035</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H90" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I90">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J90" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K90" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B91" s="1">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="D91" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="E91" s="2">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="H91" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J91" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="K91" t="s">
         <v>14</v>
@@ -4116,66 +4080,66 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B92" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D92" t="s">
         <v>13</v>
       </c>
       <c r="E92" s="2">
-        <v>3.232</v>
+        <v>0.4</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H92" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I92">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="J92" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K92" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B93" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C93" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E93" s="2">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="H93" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I93">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J93" t="s">
         <v>14</v>
@@ -4186,159 +4150,159 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B94" s="1">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D94" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E94" s="2">
-        <v>10</v>
+        <v>0.45</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G94" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H94" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I94">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="J94" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K94" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B95" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="D95" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="2">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H95" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="I95">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="J95" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="K95" t="s">
-        <v>18</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B96" s="1">
+        <v>31</v>
+      </c>
+      <c r="C96" t="s">
+        <v>19</v>
+      </c>
+      <c r="D96" t="s">
         <v>20</v>
       </c>
-      <c r="C96" t="s">
-        <v>26</v>
-      </c>
-      <c r="D96" t="s">
-        <v>13</v>
-      </c>
       <c r="E96" s="2">
-        <v>20</v>
+        <v>0.7</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H96" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I96">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="J96" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K96" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B97" s="1">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="D97" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E97" s="2">
-        <v>0.1</v>
+        <v>24</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G97" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="H97" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="J97" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="K97" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B98" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C98" t="s">
         <v>31</v>
       </c>
       <c r="D98" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E98" s="2">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>14</v>
@@ -4347,45 +4311,45 @@
         <v>33</v>
       </c>
       <c r="H98" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="I98">
-        <v>410</v>
+        <v>85</v>
       </c>
       <c r="J98" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K98" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B99" s="1">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C99" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D99" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E99" s="2">
-        <v>0.035</v>
+        <v>1</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="H99" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="J99" t="s">
         <v>14</v>
@@ -4396,34 +4360,34 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B100" s="1">
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="D100" t="s">
         <v>13</v>
       </c>
       <c r="E100" s="2">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H100" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="I100">
-        <v>74</v>
+        <v>355</v>
       </c>
       <c r="J100" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="K100" t="s">
         <v>14</v>
@@ -4431,34 +4395,34 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B101" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C101" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D101" t="s">
         <v>13</v>
       </c>
       <c r="E101" s="2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H101" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J101" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="K101" t="s">
         <v>14</v>
@@ -4466,34 +4430,34 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B102" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E102" s="2">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G102" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H102" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J102" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K102" t="s">
         <v>14</v>
@@ -4501,31 +4465,31 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B103" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="D103" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E103" s="2">
-        <v>0.45</v>
+        <v>1.7</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G103" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="H103" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I103">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J103" t="s">
         <v>14</v>
@@ -4536,80 +4500,80 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B104" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D104" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E104" s="2">
-        <v>2.3</v>
+        <v>0.1</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G104" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="H104" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I104">
-        <v>1102</v>
+        <v>50</v>
       </c>
       <c r="J104" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K104" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B105" s="1">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C105" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="D105" t="s">
         <v>13</v>
       </c>
       <c r="E105" s="2">
-        <v>5</v>
+        <v>1.41</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G105" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H105" t="s">
-        <v>146</v>
+        <v>16</v>
       </c>
       <c r="I105">
-        <v>355</v>
+        <v>230</v>
       </c>
       <c r="J105" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="K105" t="s">
-        <v>148</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B106" s="1">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C106" t="s">
         <v>19</v>
@@ -4618,7 +4582,7 @@
         <v>20</v>
       </c>
       <c r="E106" s="2">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>14</v>
@@ -4641,104 +4605,104 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B107" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D107" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E107" s="2">
-        <v>24</v>
+        <v>0.04</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H107" t="s">
-        <v>129</v>
+        <v>14</v>
       </c>
       <c r="I107">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="J107" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="K107" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B108" s="1">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C108" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D108" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E108" s="2">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H108" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="I108">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="J108" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="K108" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B109" s="1">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C109" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E109" s="2">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="H109" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="I109">
-        <v>643</v>
+        <v>85</v>
       </c>
       <c r="J109" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K109" t="s">
         <v>14</v>
@@ -4746,136 +4710,136 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B110" s="1">
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D110" t="s">
         <v>13</v>
       </c>
       <c r="E110" s="2">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G110" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H110" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I110">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="J110" t="s">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="K110" t="s">
-        <v>14</v>
+        <v>148</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B111" s="1">
         <v>5</v>
       </c>
       <c r="C111" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E111" s="2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H111" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="I111">
-        <v>74</v>
+        <v>410</v>
       </c>
       <c r="J111" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="K111" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B112" s="1">
         <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E112" s="2">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H112" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="I112">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="J112" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="K112" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B113" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="D113" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="E113" s="2">
-        <v>1.7</v>
+        <v>0.05</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="H113" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J113" t="s">
         <v>14</v>
@@ -4886,174 +4850,174 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B114" s="1">
+        <v>5</v>
+      </c>
+      <c r="C114" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="2">
+        <v>1.61</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" t="s">
+        <v>16</v>
+      </c>
+      <c r="I114">
+        <v>230</v>
+      </c>
+      <c r="J114" t="s">
         <v>17</v>
       </c>
-      <c r="C114" t="s">
-        <v>19</v>
-      </c>
-      <c r="D114" t="s">
-        <v>20</v>
-      </c>
-      <c r="E114" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G114" t="s">
-        <v>21</v>
-      </c>
-      <c r="H114" t="s">
-        <v>22</v>
-      </c>
-      <c r="I114">
-        <v>50</v>
-      </c>
-      <c r="J114" t="s">
-        <v>14</v>
-      </c>
       <c r="K114" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B115" s="1">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C115" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D115" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E115" s="2">
-        <v>1.41</v>
+        <v>0.15</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H115" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I115">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="J115" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K115" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B116" s="1">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C116" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D116" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E116" s="2">
-        <v>0.92</v>
+        <v>0.04</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="H116" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="I116">
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="J116" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K116" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B117" s="1">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C117" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D117" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E117" s="2">
-        <v>0.15</v>
+        <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G117" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H117" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I117">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="J117" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K117" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B118" s="1">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E118" s="2">
-        <v>0.04</v>
+        <v>0.7</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G118" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H118" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J118" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K118" t="s">
         <v>14</v>
@@ -5061,314 +5025,314 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B119" s="1">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C119" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="D119" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="E119" s="2">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G119" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="H119" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="I119">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J119" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K119" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B120" s="1">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D120" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E120" s="2">
-        <v>0.7</v>
+        <v>4.52</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G120" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H120" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I120">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="J120" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="K120" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B121" s="1">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C121" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="D121" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E121" s="2">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G121" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H121" t="s">
-        <v>158</v>
+        <v>22</v>
       </c>
       <c r="I121">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J121" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="K121" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B122" s="1">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D122" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E122" s="2">
-        <v>0.5</v>
+        <v>0.21</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G122" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H122" t="s">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="I122">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="J122" t="s">
-        <v>113</v>
+        <v>14</v>
       </c>
       <c r="K122" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B123" s="1">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C123" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E123" s="2">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G123" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H123" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="I123">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="J123" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="K123" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B124" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C124" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E124" s="2">
-        <v>0.05</v>
+        <v>5.82</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G124" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H124" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="I124">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="J124" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K124" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B125" s="1">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C125" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D125" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E125" s="2">
-        <v>1.61</v>
+        <v>0.6</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G125" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H125" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I125">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="J125" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K125" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B126" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C126" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D126" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E126" s="2">
-        <v>0.92</v>
+        <v>0.13</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G126" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="H126" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="I126">
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="J126" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K126" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B127" s="1">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C127" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E127" s="2">
-        <v>0.15</v>
+        <v>3.5</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G127" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H127" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I127">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="J127" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K127" t="s">
         <v>14</v>
@@ -5376,31 +5340,31 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B128" s="1">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C128" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="D128" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E128" s="2">
-        <v>0.04</v>
+        <v>5</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="H128" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="s">
         <v>14</v>
@@ -5411,69 +5375,69 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B129" s="1">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E129" s="2">
-        <v>9</v>
+        <v>0.24</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G129" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H129" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I129">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="J129" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K129" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B130" s="1">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C130" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E130" s="2">
-        <v>0.7</v>
+        <v>0.012</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G130" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H130" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="I130">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J130" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K130" t="s">
         <v>14</v>
@@ -5481,34 +5445,34 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B131" s="1">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C131" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="D131" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E131" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G131" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="H131" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="I131">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J131" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="K131" t="s">
         <v>14</v>
@@ -5516,80 +5480,80 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B132" s="1">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C132" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D132" t="s">
         <v>13</v>
       </c>
       <c r="E132" s="2">
-        <v>4.52</v>
+        <v>14</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G132" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H132" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="I132">
-        <v>230</v>
+        <v>4</v>
       </c>
       <c r="J132" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K132" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B133" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C133" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="D133" t="s">
         <v>13</v>
       </c>
       <c r="E133" s="2">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G133" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="H133" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="I133">
-        <v>1102</v>
+        <v>230</v>
       </c>
       <c r="J133" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="K133" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B134" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C134" t="s">
         <v>19</v>
@@ -5598,7 +5562,7 @@
         <v>20</v>
       </c>
       <c r="E134" s="2">
-        <v>0.6</v>
+        <v>0.24</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>14</v>
@@ -5621,10 +5585,10 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B135" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C135" t="s">
         <v>23</v>
@@ -5633,7 +5597,7 @@
         <v>24</v>
       </c>
       <c r="E135" s="2">
-        <v>0.21</v>
+        <v>0.012</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>14</v>
@@ -5656,34 +5620,34 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B136" s="1">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C136" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D136" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E136" s="2">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G136" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="H136" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="I136">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J136" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K136" t="s">
         <v>14</v>
@@ -5691,7 +5655,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B137" s="1">
         <v>5</v>
@@ -5703,7 +5667,7 @@
         <v>13</v>
       </c>
       <c r="E137" s="2">
-        <v>5.82</v>
+        <v>0.5</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>14</v>
@@ -5726,66 +5690,66 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B138" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C138" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E138" s="2">
-        <v>3.4</v>
+        <v>0.24</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="H138" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="I138">
-        <v>1102</v>
+        <v>50</v>
       </c>
       <c r="J138" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="K138" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B139" s="1">
+        <v>23</v>
+      </c>
+      <c r="C139" t="s">
+        <v>23</v>
+      </c>
+      <c r="D139" t="s">
         <v>24</v>
       </c>
-      <c r="C139" t="s">
-        <v>19</v>
-      </c>
-      <c r="D139" t="s">
-        <v>20</v>
-      </c>
       <c r="E139" s="2">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H139" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I139">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J139" t="s">
         <v>14</v>
@@ -5796,34 +5760,34 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B140" s="1">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C140" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="D140" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E140" s="2">
-        <v>0.13</v>
+        <v>8</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="H140" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J140" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="K140" t="s">
         <v>14</v>
@@ -5831,66 +5795,66 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B141" s="1">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C141" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D141" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E141" s="2">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H141" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I141">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="J141" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K141" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B142" s="1">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="C142" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="D142" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="E142" s="2">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H142" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="I142">
-        <v>1</v>
+        <v>355</v>
       </c>
       <c r="J142" t="s">
         <v>14</v>
@@ -5901,631 +5865,36 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B143" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D143" t="s">
         <v>13</v>
       </c>
       <c r="E143" s="2">
-        <v>35.6</v>
+        <v>0.38</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G143" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H143" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="I143">
-        <v>1102</v>
+        <v>74</v>
       </c>
       <c r="J143" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K143" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>164</v>
-      </c>
-      <c r="B144" s="1">
-        <v>14</v>
-      </c>
-      <c r="C144" t="s">
-        <v>19</v>
-      </c>
-      <c r="D144" t="s">
-        <v>20</v>
-      </c>
-      <c r="E144" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G144" t="s">
-        <v>21</v>
-      </c>
-      <c r="H144" t="s">
-        <v>22</v>
-      </c>
-      <c r="I144">
-        <v>50</v>
-      </c>
-      <c r="J144" t="s">
-        <v>14</v>
-      </c>
-      <c r="K144" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>164</v>
-      </c>
-      <c r="B145" s="1">
-        <v>23</v>
-      </c>
-      <c r="C145" t="s">
-        <v>23</v>
-      </c>
-      <c r="D145" t="s">
-        <v>24</v>
-      </c>
-      <c r="E145" s="2">
-        <v>0.012</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G145" t="s">
-        <v>25</v>
-      </c>
-      <c r="H145" t="s">
-        <v>14</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145" t="s">
-        <v>14</v>
-      </c>
-      <c r="K145" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>164</v>
-      </c>
-      <c r="B146" s="1">
-        <v>29</v>
-      </c>
-      <c r="C146" t="s">
-        <v>165</v>
-      </c>
-      <c r="D146" t="s">
-        <v>66</v>
-      </c>
-      <c r="E146" s="2">
-        <v>8</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G146" t="s">
-        <v>84</v>
-      </c>
-      <c r="H146" t="s">
-        <v>166</v>
-      </c>
-      <c r="I146">
-        <v>6</v>
-      </c>
-      <c r="J146" t="s">
-        <v>167</v>
-      </c>
-      <c r="K146" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>164</v>
-      </c>
-      <c r="B147" s="1">
-        <v>31</v>
-      </c>
-      <c r="C147" t="s">
-        <v>26</v>
-      </c>
-      <c r="D147" t="s">
-        <v>13</v>
-      </c>
-      <c r="E147" s="2">
-        <v>14</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G147" t="s">
-        <v>27</v>
-      </c>
-      <c r="H147" t="s">
-        <v>28</v>
-      </c>
-      <c r="I147">
-        <v>4</v>
-      </c>
-      <c r="J147" t="s">
-        <v>29</v>
-      </c>
-      <c r="K147" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>168</v>
-      </c>
-      <c r="B148" s="1">
-        <v>5</v>
-      </c>
-      <c r="C148" t="s">
-        <v>12</v>
-      </c>
-      <c r="D148" t="s">
-        <v>13</v>
-      </c>
-      <c r="E148" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="F148" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G148" t="s">
-        <v>15</v>
-      </c>
-      <c r="H148" t="s">
-        <v>16</v>
-      </c>
-      <c r="I148">
-        <v>230</v>
-      </c>
-      <c r="J148" t="s">
-        <v>17</v>
-      </c>
-      <c r="K148" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>168</v>
-      </c>
-      <c r="B149" s="1">
-        <v>8</v>
-      </c>
-      <c r="C149" t="s">
-        <v>57</v>
-      </c>
-      <c r="D149" t="s">
-        <v>13</v>
-      </c>
-      <c r="E149" s="2">
-        <v>3</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G149" t="s">
-        <v>58</v>
-      </c>
-      <c r="H149" t="s">
-        <v>77</v>
-      </c>
-      <c r="I149">
-        <v>1102</v>
-      </c>
-      <c r="J149" t="s">
-        <v>60</v>
-      </c>
-      <c r="K149" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>168</v>
-      </c>
-      <c r="B150" s="1">
-        <v>15</v>
-      </c>
-      <c r="C150" t="s">
-        <v>19</v>
-      </c>
-      <c r="D150" t="s">
-        <v>20</v>
-      </c>
-      <c r="E150" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" t="s">
-        <v>21</v>
-      </c>
-      <c r="H150" t="s">
-        <v>22</v>
-      </c>
-      <c r="I150">
-        <v>50</v>
-      </c>
-      <c r="J150" t="s">
-        <v>14</v>
-      </c>
-      <c r="K150" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>168</v>
-      </c>
-      <c r="B151" s="1">
-        <v>24</v>
-      </c>
-      <c r="C151" t="s">
-        <v>23</v>
-      </c>
-      <c r="D151" t="s">
-        <v>24</v>
-      </c>
-      <c r="E151" s="2">
-        <v>0.012</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G151" t="s">
-        <v>25</v>
-      </c>
-      <c r="H151" t="s">
-        <v>14</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151" t="s">
-        <v>14</v>
-      </c>
-      <c r="K151" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>168</v>
-      </c>
-      <c r="B152" s="1">
-        <v>33</v>
-      </c>
-      <c r="C152" t="s">
-        <v>153</v>
-      </c>
-      <c r="D152" t="s">
-        <v>66</v>
-      </c>
-      <c r="E152" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G152" t="s">
-        <v>154</v>
-      </c>
-      <c r="H152" t="s">
-        <v>14</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152" t="s">
-        <v>14</v>
-      </c>
-      <c r="K152" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>169</v>
-      </c>
-      <c r="B153" s="1">
-        <v>5</v>
-      </c>
-      <c r="C153" t="s">
-        <v>12</v>
-      </c>
-      <c r="D153" t="s">
-        <v>13</v>
-      </c>
-      <c r="E153" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F153" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G153" t="s">
-        <v>15</v>
-      </c>
-      <c r="H153" t="s">
-        <v>16</v>
-      </c>
-      <c r="I153">
-        <v>230</v>
-      </c>
-      <c r="J153" t="s">
-        <v>17</v>
-      </c>
-      <c r="K153" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>169</v>
-      </c>
-      <c r="B154" s="1">
-        <v>8</v>
-      </c>
-      <c r="C154" t="s">
-        <v>57</v>
-      </c>
-      <c r="D154" t="s">
-        <v>13</v>
-      </c>
-      <c r="E154" s="2">
-        <v>5.8</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G154" t="s">
-        <v>58</v>
-      </c>
-      <c r="H154" t="s">
-        <v>77</v>
-      </c>
-      <c r="I154">
-        <v>1102</v>
-      </c>
-      <c r="J154" t="s">
-        <v>60</v>
-      </c>
-      <c r="K154" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>169</v>
-      </c>
-      <c r="B155" s="1">
-        <v>13</v>
-      </c>
-      <c r="C155" t="s">
-        <v>19</v>
-      </c>
-      <c r="D155" t="s">
-        <v>20</v>
-      </c>
-      <c r="E155" s="2">
-        <v>0.24</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G155" t="s">
-        <v>21</v>
-      </c>
-      <c r="H155" t="s">
-        <v>22</v>
-      </c>
-      <c r="I155">
-        <v>50</v>
-      </c>
-      <c r="J155" t="s">
-        <v>14</v>
-      </c>
-      <c r="K155" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>169</v>
-      </c>
-      <c r="B156" s="1">
-        <v>23</v>
-      </c>
-      <c r="C156" t="s">
-        <v>23</v>
-      </c>
-      <c r="D156" t="s">
-        <v>24</v>
-      </c>
-      <c r="E156" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G156" t="s">
-        <v>25</v>
-      </c>
-      <c r="H156" t="s">
-        <v>14</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
-      <c r="J156" t="s">
-        <v>14</v>
-      </c>
-      <c r="K156" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>169</v>
-      </c>
-      <c r="B157" s="1">
-        <v>29</v>
-      </c>
-      <c r="C157" t="s">
-        <v>165</v>
-      </c>
-      <c r="D157" t="s">
-        <v>66</v>
-      </c>
-      <c r="E157" s="2">
-        <v>8</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G157" t="s">
-        <v>84</v>
-      </c>
-      <c r="H157" t="s">
-        <v>166</v>
-      </c>
-      <c r="I157">
-        <v>6</v>
-      </c>
-      <c r="J157" t="s">
-        <v>167</v>
-      </c>
-      <c r="K157" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>169</v>
-      </c>
-      <c r="B158" s="1">
-        <v>31</v>
-      </c>
-      <c r="C158" t="s">
-        <v>26</v>
-      </c>
-      <c r="D158" t="s">
-        <v>13</v>
-      </c>
-      <c r="E158" s="2">
-        <v>7</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G158" t="s">
-        <v>27</v>
-      </c>
-      <c r="H158" t="s">
-        <v>28</v>
-      </c>
-      <c r="I158">
-        <v>4</v>
-      </c>
-      <c r="J158" t="s">
-        <v>29</v>
-      </c>
-      <c r="K158" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>170</v>
-      </c>
-      <c r="B159" s="1">
-        <v>3</v>
-      </c>
-      <c r="C159" t="s">
-        <v>151</v>
-      </c>
-      <c r="D159" t="s">
-        <v>13</v>
-      </c>
-      <c r="E159" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G159" t="s">
-        <v>44</v>
-      </c>
-      <c r="H159" t="s">
-        <v>171</v>
-      </c>
-      <c r="I159">
-        <v>355</v>
-      </c>
-      <c r="J159" t="s">
-        <v>14</v>
-      </c>
-      <c r="K159" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>170</v>
-      </c>
-      <c r="B160" s="1">
-        <v>4</v>
-      </c>
-      <c r="C160" t="s">
-        <v>37</v>
-      </c>
-      <c r="D160" t="s">
-        <v>13</v>
-      </c>
-      <c r="E160" s="2">
-        <v>0.38</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G160" t="s">
-        <v>38</v>
-      </c>
-      <c r="H160" t="s">
-        <v>39</v>
-      </c>
-      <c r="I160">
-        <v>74</v>
-      </c>
-      <c r="J160" t="s">
-        <v>40</v>
-      </c>
-      <c r="K160" t="s">
         <v>14</v>
       </c>
     </row>
